--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17935" uniqueCount="1695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17937" uniqueCount="1695">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5437,7 +5437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B316"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -5817,89 +5817,89 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="1">
+      <c r="A49" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B49" t="s" s="1">
+      <c r="B50" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>12</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B56" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -5907,169 +5907,169 @@
         <v>18</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>117</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B63" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>117</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>36</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B70" t="s" s="2">
+      <c r="B71" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="s" s="1">
+    <row r="72">
+      <c r="A72" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B71" t="s" s="1">
+      <c r="B72" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>7</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>12</v>
+        <v>440</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B78" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -6077,169 +6077,169 @@
         <v>18</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>440</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B85" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>440</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>441</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>36</v>
+        <v>442</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B92" t="s" s="2">
+      <c r="B93" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="s" s="1">
+    <row r="94">
+      <c r="A94" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B93" t="s" s="1">
+      <c r="B94" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>708</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>7</v>
+        <v>709</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>708</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>457</v>
+        <v>708</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>12</v>
+        <v>457</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B100" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104">
@@ -6247,177 +6247,177 @@
         <v>18</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>458</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B107" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>458</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B115" t="s" s="2">
+      <c r="B116" t="s" s="2">
         <v>710</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="s" s="1">
+    <row r="117">
+      <c r="A117" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B116" t="s" s="1">
+      <c r="B117" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>712</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>7</v>
+        <v>713</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>712</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>12</v>
+        <v>714</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B123" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127">
@@ -6425,169 +6425,169 @@
         <v>18</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>715</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B130" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>715</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>716</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>36</v>
+        <v>717</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B137" t="s" s="2">
+      <c r="B138" t="s" s="2">
         <v>718</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="s" s="1">
+    <row r="139">
+      <c r="A139" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B138" t="s" s="1">
+      <c r="B139" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>738</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>7</v>
+        <v>739</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>738</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>12</v>
+        <v>740</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B145" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149">
@@ -6595,169 +6595,169 @@
         <v>18</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>741</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B152" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>741</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>742</v>
+        <v>118</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>36</v>
+        <v>743</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B159" t="s" s="2">
+      <c r="B160" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="s" s="1">
+    <row r="161">
+      <c r="A161" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B160" t="s" s="1">
+      <c r="B161" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>878</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>7</v>
+        <v>879</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>878</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>12</v>
+        <v>880</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B167" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171">
@@ -6765,169 +6765,169 @@
         <v>18</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>881</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B174" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>881</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>716</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>879</v>
+        <v>716</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>717</v>
+        <v>879</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>36</v>
+        <v>717</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B181" t="s" s="2">
+      <c r="B182" t="s" s="2">
         <v>718</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="s" s="1">
+    <row r="183">
+      <c r="A183" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B182" t="s" s="1">
+      <c r="B183" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>905</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>7</v>
+        <v>906</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>905</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>12</v>
+        <v>907</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B189" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193">
@@ -6935,169 +6935,169 @@
         <v>18</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>908</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B196" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>908</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>742</v>
+        <v>118</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>36</v>
+        <v>743</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B203" t="s" s="2">
+      <c r="B204" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="s" s="1">
+    <row r="205">
+      <c r="A205" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B204" t="s" s="1">
+      <c r="B205" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>909</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>7</v>
+        <v>910</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>909</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>12</v>
+        <v>911</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B211" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="215">
@@ -7105,169 +7105,169 @@
         <v>18</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>912</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B218" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>912</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>913</v>
+        <v>118</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>36</v>
+        <v>914</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B225" t="s" s="2">
+      <c r="B226" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="s" s="1">
+    <row r="227">
+      <c r="A227" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B226" t="s" s="1">
+      <c r="B227" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>1059</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>7</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>1059</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>12</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B233" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237">
@@ -7275,169 +7275,169 @@
         <v>18</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>1062</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B240" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>1062</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>1063</v>
+        <v>118</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>36</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B247" t="s" s="2">
+      <c r="B248" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="s" s="1">
+    <row r="249">
+      <c r="A249" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B248" t="s" s="1">
+      <c r="B249" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>1271</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>7</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>1271</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>12</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B255" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259">
@@ -7445,169 +7445,169 @@
         <v>18</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>1274</v>
+        <v>22</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B262" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>1274</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B264" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>1275</v>
+        <v>118</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>36</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B269" t="s" s="2">
+      <c r="B270" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="s" s="1">
+    <row r="271">
+      <c r="A271" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B270" t="s" s="1">
+      <c r="B271" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B271" t="s" s="2">
-        <v>1489</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>7</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>1489</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>12</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B277" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B278" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281">
@@ -7615,169 +7615,169 @@
         <v>18</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>1492</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B284" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>1492</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B286" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>1493</v>
+        <v>118</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>36</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B291" t="s" s="2">
+      <c r="B292" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="s" s="1">
+    <row r="293">
+      <c r="A293" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B292" t="s" s="1">
+      <c r="B293" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B293" t="s" s="2">
-        <v>1659</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>7</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>1659</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>1457</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>12</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B299" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B300" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="303">
@@ -7785,91 +7785,91 @@
         <v>18</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>938</v>
+        <v>22</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B306" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>938</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B308" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>1661</v>
+        <v>38</v>
       </c>
     </row>
     <row r="315">
@@ -7877,7 +7877,7 @@
         <v>39</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="316">
@@ -7885,6 +7885,14 @@
         <v>39</v>
       </c>
       <c r="B316" t="s" s="2">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B317" t="s" s="2">
         <v>1663</v>
       </c>
     </row>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/all-profiles.xlsx
+++ b/branches/sandbox/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
